--- a/excel/output_stats_vfvv/covariance/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/covariance/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>58</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -823,10 +823,10 @@
         <v>0.6</v>
       </c>
       <c r="N8" t="n">
-        <v>345.41</v>
+        <v>346.161</v>
       </c>
       <c r="O8" t="n">
-        <v>347.7</v>
+        <v>348.45</v>
       </c>
     </row>
     <row r="9">
@@ -870,10 +870,10 @@
         <v>0.6</v>
       </c>
       <c r="N9" t="n">
-        <v>345.409</v>
+        <v>346.161</v>
       </c>
       <c r="O9" t="n">
-        <v>354.55</v>
+        <v>355.62</v>
       </c>
     </row>
     <row r="10">
@@ -917,10 +917,10 @@
         <v>0.6</v>
       </c>
       <c r="N10" t="n">
-        <v>352.335</v>
+        <v>353.447</v>
       </c>
       <c r="O10" t="n">
-        <v>355.42</v>
+        <v>356.55</v>
       </c>
     </row>
     <row r="11">
@@ -964,10 +964,10 @@
         <v>0.6</v>
       </c>
       <c r="N11" t="n">
-        <v>352.335</v>
+        <v>353.447</v>
       </c>
       <c r="O11" t="n">
-        <v>355.51</v>
+        <v>356.67</v>
       </c>
     </row>
     <row r="12">
@@ -1011,10 +1011,10 @@
         <v>0.6</v>
       </c>
       <c r="N12" t="n">
-        <v>351.261</v>
+        <v>352.374</v>
       </c>
       <c r="O12" t="n">
-        <v>354.12</v>
+        <v>355.33</v>
       </c>
     </row>
     <row r="13">
@@ -1058,10 +1058,10 @@
         <v>0.6</v>
       </c>
       <c r="N13" t="n">
-        <v>351.26</v>
+        <v>352.374</v>
       </c>
       <c r="O13" t="n">
-        <v>354.11</v>
+        <v>355.32</v>
       </c>
     </row>
     <row r="14">
@@ -1069,37 +1069,37 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>1.12309e-09</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.61111e-09</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.311009</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4.05559e-18</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1107690000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3600000000</v>
+        <v>3100000000</v>
       </c>
       <c r="M14" t="n">
         <v>0.6</v>
@@ -1116,34 +1116,34 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00124838</v>
+        <v>1.12309e-09</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00431372</v>
+        <v>3.61111e-09</v>
       </c>
       <c r="E15" t="n">
-        <v>0.289397</v>
+        <v>0.311009</v>
       </c>
       <c r="F15" t="n">
-        <v>5.38514e-06</v>
+        <v>4.05559e-18</v>
       </c>
       <c r="G15" t="n">
-        <v>876413000</v>
+        <v>1107690000</v>
       </c>
       <c r="H15" t="n">
-        <v>3780600</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1681200</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>15529400</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>3600000000</v>
@@ -1155,7 +1155,7 @@
         <v>351.252</v>
       </c>
       <c r="O15" t="n">
-        <v>353.75</v>
+        <v>353.76</v>
       </c>
     </row>
     <row r="16">
@@ -1163,34 +1163,34 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>1.76354e-09</v>
+        <v>0.00124838</v>
       </c>
       <c r="D16" t="n">
-        <v>5.83333e-09</v>
+        <v>0.00431372</v>
       </c>
       <c r="E16" t="n">
-        <v>0.302321</v>
+        <v>0.289397</v>
       </c>
       <c r="F16" t="n">
-        <v>1.02873e-17</v>
+        <v>5.38514e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>857143000</v>
+        <v>876413000</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3780600</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2940000</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>15529400</v>
       </c>
       <c r="L16" t="n">
         <v>3600000000</v>
@@ -1199,10 +1199,10 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>350.153</v>
+        <v>351.252</v>
       </c>
       <c r="O16" t="n">
-        <v>350.33</v>
+        <v>353.75</v>
       </c>
     </row>
     <row r="17">
@@ -1210,34 +1210,34 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1.03825e-09</v>
+        <v>1.76354e-09</v>
       </c>
       <c r="D17" t="n">
-        <v>3.61111e-09</v>
+        <v>5.83333e-09</v>
       </c>
       <c r="E17" t="n">
-        <v>0.287515</v>
+        <v>0.302321</v>
       </c>
       <c r="F17" t="n">
-        <v>3.74923e-18</v>
+        <v>1.02873e-17</v>
       </c>
       <c r="G17" t="n">
-        <v>830769000</v>
+        <v>857143000</v>
       </c>
       <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L17" t="n">
         <v>3600000000</v>
@@ -1257,34 +1257,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>2.31827e-10</v>
+        <v>1.03825e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>5.55556e-10</v>
+        <v>3.61111e-09</v>
       </c>
       <c r="E18" t="n">
-        <v>0.417289</v>
+        <v>0.287515</v>
       </c>
       <c r="F18" t="n">
-        <v>1.28793e-19</v>
+        <v>3.74923e-18</v>
       </c>
       <c r="G18" t="n">
-        <v>3600000000</v>
+        <v>830769000</v>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
         <v>3600000000</v>
@@ -1293,10 +1293,10 @@
         <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>350.152</v>
+        <v>350.153</v>
       </c>
       <c r="O18" t="n">
-        <v>350.32</v>
+        <v>350.33</v>
       </c>
     </row>
     <row r="19">
@@ -1304,34 +1304,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>1.81663e-09</v>
+        <v>2.31827e-10</v>
       </c>
       <c r="D19" t="n">
-        <v>5.55556e-09</v>
+        <v>5.55556e-10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.326994</v>
+        <v>0.417289</v>
       </c>
       <c r="F19" t="n">
-        <v>1.00924e-17</v>
+        <v>1.28793e-19</v>
       </c>
       <c r="G19" t="n">
-        <v>1440000000</v>
+        <v>3600000000</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>3600000000</v>
@@ -1343,7 +1343,7 @@
         <v>350.152</v>
       </c>
       <c r="O19" t="n">
-        <v>350.25</v>
+        <v>350.32</v>
       </c>
     </row>
     <row r="20">
@@ -1351,34 +1351,34 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>4.80793e-10</v>
+        <v>1.81663e-09</v>
       </c>
       <c r="D20" t="n">
-        <v>1.38889e-09</v>
+        <v>5.55556e-09</v>
       </c>
       <c r="E20" t="n">
-        <v>0.346171</v>
+        <v>0.326994</v>
       </c>
       <c r="F20" t="n">
-        <v>6.67768e-19</v>
+        <v>1.00924e-17</v>
       </c>
       <c r="G20" t="n">
-        <v>2160000000</v>
+        <v>1440000000</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L20" t="n">
         <v>3600000000</v>
@@ -1387,10 +1387,10 @@
         <v>0.6</v>
       </c>
       <c r="N20" t="n">
-        <v>350.151</v>
+        <v>350.152</v>
       </c>
       <c r="O20" t="n">
-        <v>350.22</v>
+        <v>350.25</v>
       </c>
     </row>
     <row r="21">
@@ -1398,34 +1398,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>4.9425e-09</v>
+        <v>4.80793e-10</v>
       </c>
       <c r="D21" t="n">
-        <v>1.69444e-08</v>
+        <v>1.38889e-09</v>
       </c>
       <c r="E21" t="n">
-        <v>0.291689</v>
+        <v>0.346171</v>
       </c>
       <c r="F21" t="n">
-        <v>8.3748e-17</v>
+        <v>6.67768e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>826229000</v>
+        <v>2160000000</v>
       </c>
       <c r="H21" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>3600000000</v>
@@ -1434,10 +1434,10 @@
         <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O21" t="n">
-        <v>350.17</v>
+        <v>350.22</v>
       </c>
     </row>
     <row r="22">
@@ -1445,34 +1445,34 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>4.64603e-10</v>
+        <v>4.9425e-09</v>
       </c>
       <c r="D22" t="n">
-        <v>1.66667e-09</v>
+        <v>1.69444e-08</v>
       </c>
       <c r="E22" t="n">
-        <v>0.278762</v>
+        <v>0.291689</v>
       </c>
       <c r="F22" t="n">
-        <v>7.74338e-19</v>
+        <v>8.3748e-17</v>
       </c>
       <c r="G22" t="n">
-        <v>600000000</v>
+        <v>826229000</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="L22" t="n">
         <v>3600000000</v>
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
         <v>4.64603e-10</v>
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>6.10341e-10</v>
+        <v>4.64603e-10</v>
       </c>
       <c r="D24" t="n">
-        <v>1.94444e-09</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E24" t="n">
-        <v>0.31389</v>
+        <v>0.278762</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18677e-18</v>
+        <v>7.74338e-19</v>
       </c>
       <c r="G24" t="n">
-        <v>1028570000</v>
+        <v>600000000</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>3600000000</v>
@@ -1575,10 +1575,10 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O24" t="n">
-        <v>350.18</v>
+        <v>350.17</v>
       </c>
     </row>
     <row r="25">
@@ -1586,7 +1586,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
         <v>6.10341e-10</v>
@@ -1633,34 +1633,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>1.45203e-09</v>
+        <v>6.10341e-10</v>
       </c>
       <c r="D26" t="n">
-        <v>4.72222e-09</v>
+        <v>1.94444e-09</v>
       </c>
       <c r="E26" t="n">
-        <v>0.30749</v>
+        <v>0.31389</v>
       </c>
       <c r="F26" t="n">
-        <v>6.85683e-18</v>
+        <v>1.18677e-18</v>
       </c>
       <c r="G26" t="n">
-        <v>847059000</v>
+        <v>1028570000</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
         <v>3600000000</v>
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>1.19266e-10</v>
+        <v>1.45203e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>2.77778e-10</v>
+        <v>4.72222e-09</v>
       </c>
       <c r="E27" t="n">
-        <v>0.429359</v>
+        <v>0.30749</v>
       </c>
       <c r="F27" t="n">
-        <v>3.31295e-20</v>
+        <v>6.85683e-18</v>
       </c>
       <c r="G27" t="n">
-        <v>3600000000</v>
+        <v>847059000</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
         <v>3600000000</v>
@@ -1719,6 +1719,53 @@
         <v>350.151</v>
       </c>
       <c r="O27" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.19266e-10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.77778e-10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.429359</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.31295e-20</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O28" t="n">
         <v>350.23</v>
       </c>
     </row>
